--- a/Configs/GameConfig/Datas/fg/#RecipeIo-配方行.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RecipeIo-配方行.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>drop_pod</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1335,16 +1335,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>drop_pod</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1359,27 +1359,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>drop_pod</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>drop_pod</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1404</v>
+        <v>1501</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>combat_component</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1405</v>
+        <v>1502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1412,35 +1412,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>part</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>megastructure_part</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>precision_part</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1451,20 +1451,20 @@
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>megastructure_part</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>combat_component</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1475,31 +1475,31 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>megastructure_part</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1504</v>
+        <v>1601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>coolant</t>
+          <t>precision_part</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1505</v>
+        <v>1602</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1532,13 +1532,85 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>megastructure_part</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>electronic</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>1604</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>megastructure_part</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>coolant</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>200</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>1605</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>megastructure_part</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>megastructure_part</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>out</t>
         </is>
